--- a/data/dividends_info_20260324.xlsx
+++ b/data/dividends_info_20260324.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.54999923706055</v>
+        <v>49.97999954223633</v>
       </c>
       <c r="I2" t="n">
-        <v>1.384767577774358</v>
+        <v>1.400560236917279</v>
       </c>
       <c r="J2" t="n">
         <v>335</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.960000038146973</v>
+        <v>1.952000021934509</v>
       </c>
       <c r="I3" t="n">
-        <v>3.928571352110661</v>
+        <v>3.944672086821493</v>
       </c>
       <c r="J3" t="n">
         <v>244</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.449999809265137</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I4" t="n">
-        <v>3.669724899072381</v>
+        <v>3.703703638293944</v>
       </c>
       <c r="J4" t="n">
         <v>237</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9.067000389099121</v>
+        <v>9.208000183105469</v>
       </c>
       <c r="I5" t="n">
-        <v>2.867541511441725</v>
+        <v>2.823631568524937</v>
       </c>
       <c r="J5" t="n">
         <v>118</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>18.39999961853027</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04347830323506</v>
+        <v>2.088888888888889</v>
       </c>
       <c r="J6" t="n">
         <v>118</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4.414999961853027</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="I7" t="n">
-        <v>2.718006818501411</v>
+        <v>2.708803716703606</v>
       </c>
       <c r="J7" t="n">
         <v>111</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>30.20000076293945</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.4966887291740587</v>
       </c>
       <c r="J9" t="n">
         <v>104</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21.73999977111816</v>
+        <v>21.8799991607666</v>
       </c>
       <c r="I10" t="n">
-        <v>4.369825252997867</v>
+        <v>4.341864883173583</v>
       </c>
       <c r="J10" t="n">
         <v>90</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>20.70000076293945</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9420289507869057</v>
+        <v>0.9466019242184478</v>
       </c>
       <c r="J11" t="n">
         <v>90</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.447999954223633</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="I12" t="n">
-        <v>5.661764811754503</v>
+        <v>5.823529131743689</v>
       </c>
       <c r="J12" t="n">
         <v>90</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>59.20000076293945</v>
+        <v>57.97999954223633</v>
       </c>
       <c r="I13" t="n">
-        <v>1.064189175474461</v>
+        <v>1.086581588433901</v>
       </c>
       <c r="J13" t="n">
         <v>90</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>15.64999961853027</v>
+        <v>15.94999980926514</v>
       </c>
       <c r="I14" t="n">
-        <v>4.984025680591368</v>
+        <v>4.890282190140897</v>
       </c>
       <c r="J14" t="n">
         <v>90</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>19.97999954223633</v>
+        <v>19.92000007629395</v>
       </c>
       <c r="I15" t="n">
-        <v>4.254254351723878</v>
+        <v>4.267068256749424</v>
       </c>
       <c r="J15" t="n">
         <v>90</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6.254000186920166</v>
+        <v>6.315999984741211</v>
       </c>
       <c r="I16" t="n">
-        <v>2.898944588763798</v>
+        <v>2.870487657346448</v>
       </c>
       <c r="J16" t="n">
         <v>90</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7.75</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I17" t="n">
-        <v>3.354838709677419</v>
+        <v>3.443708522273474</v>
       </c>
       <c r="J17" t="n">
         <v>90</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>25.64999961853027</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="I18" t="n">
-        <v>4.327485444475817</v>
+        <v>4.319066019642573</v>
       </c>
       <c r="J18" t="n">
         <v>72</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8270000219345093</v>
       </c>
       <c r="I19" t="n">
-        <v>3.658536617277918</v>
+        <v>3.627569432201989</v>
       </c>
       <c r="J19" t="n">
         <v>69</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4679999947547913</v>
       </c>
       <c r="I20" t="n">
-        <v>4.999999909297282</v>
+        <v>4.914529969610546</v>
       </c>
       <c r="J20" t="n">
         <v>69</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>11.77000045776367</v>
+        <v>11.86999988555908</v>
       </c>
       <c r="I21" t="n">
-        <v>2.124044097509751</v>
+        <v>2.106149978182791</v>
       </c>
       <c r="J21" t="n">
         <v>62</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="I22" t="n">
-        <v>4.285714285714286</v>
+        <v>4.261363659454279</v>
       </c>
       <c r="J22" t="n">
         <v>62</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.305000066757202</v>
+        <v>2.348000049591064</v>
       </c>
       <c r="I23" t="n">
-        <v>4.511930455009174</v>
+        <v>4.429301439670454</v>
       </c>
       <c r="J23" t="n">
         <v>55</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>8.399999618530273</v>
+        <v>8.744000434875488</v>
       </c>
       <c r="I24" t="n">
-        <v>3.452381109164151</v>
+        <v>3.316559761860642</v>
       </c>
       <c r="J24" t="n">
         <v>55</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.960000038146973</v>
+        <v>1.952000021934509</v>
       </c>
       <c r="I25" t="n">
-        <v>3.928571352110661</v>
+        <v>3.944672086821493</v>
       </c>
       <c r="J25" t="n">
         <v>55</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>33.34000015258789</v>
+        <v>33.2599983215332</v>
       </c>
       <c r="I26" t="n">
-        <v>4.919016174247681</v>
+        <v>4.930848114139051</v>
       </c>
       <c r="J26" t="n">
         <v>55</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>32.38000106811523</v>
+        <v>32.36999893188477</v>
       </c>
       <c r="I27" t="n">
-        <v>6.176652050729581</v>
+        <v>6.178560599302277</v>
       </c>
       <c r="J27" t="n">
         <v>55</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3.638000011444092</v>
+        <v>3.742000102996826</v>
       </c>
       <c r="I28" t="n">
-        <v>2.748763047977708</v>
+        <v>2.672367644242281</v>
       </c>
       <c r="J28" t="n">
         <v>55</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>34.79999923706055</v>
+        <v>33.09999847412109</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4266092047550861</v>
+        <v>0.4485196581385705</v>
       </c>
       <c r="J29" t="n">
         <v>55</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>22.23999977111816</v>
+        <v>21.95999908447266</v>
       </c>
       <c r="I30" t="n">
-        <v>4.136690690054558</v>
+        <v>4.189435511636738</v>
       </c>
       <c r="J30" t="n">
         <v>55</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>7.639999866485596</v>
+        <v>7.764999866485596</v>
       </c>
       <c r="I31" t="n">
-        <v>3.926701639302517</v>
+        <v>3.863490085747788</v>
       </c>
       <c r="J31" t="n">
         <v>55</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>73.81999969482422</v>
+        <v>72.83999633789062</v>
       </c>
       <c r="I32" t="n">
-        <v>1.408832300595252</v>
+        <v>1.427787002041628</v>
       </c>
       <c r="J32" t="n">
         <v>55</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>50.54999923706055</v>
+        <v>49.97999954223633</v>
       </c>
       <c r="I33" t="n">
-        <v>4.352126673005126</v>
+        <v>4.401760744597162</v>
       </c>
       <c r="J33" t="n">
         <v>55</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7.254000186920166</v>
+        <v>7.342999935150146</v>
       </c>
       <c r="I34" t="n">
-        <v>11.85552767906849</v>
+        <v>11.71183450354225</v>
       </c>
       <c r="J34" t="n">
         <v>55</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10.83500003814697</v>
+        <v>10.85999965667725</v>
       </c>
       <c r="I35" t="n">
-        <v>5.168435607091816</v>
+        <v>5.156537916239117</v>
       </c>
       <c r="J35" t="n">
         <v>55</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.759999990463257</v>
+        <v>1.754999995231628</v>
       </c>
       <c r="I36" t="n">
-        <v>2.272727285042282</v>
+        <v>2.279202285394919</v>
       </c>
       <c r="J36" t="n">
         <v>55</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>8.699999809265137</v>
+        <v>8.619999885559082</v>
       </c>
       <c r="I37" t="n">
-        <v>3.448275937667407</v>
+        <v>3.480278468478685</v>
       </c>
       <c r="J37" t="n">
         <v>55</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.289999961853027</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I38" t="n">
-        <v>4.716157283802238</v>
+        <v>4.757709291077578</v>
       </c>
       <c r="J38" t="n">
         <v>55</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>61.90000152587891</v>
+        <v>61.09999847412109</v>
       </c>
       <c r="I39" t="n">
-        <v>3.327948221679386</v>
+        <v>3.371522179124952</v>
       </c>
       <c r="J39" t="n">
         <v>55</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>14.35999965667725</v>
+        <v>14.19999980926514</v>
       </c>
       <c r="I40" t="n">
-        <v>5.222841350495841</v>
+        <v>5.281690211788906</v>
       </c>
       <c r="J40" t="n">
         <v>55</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>15.07999992370605</v>
+        <v>15.23999977111816</v>
       </c>
       <c r="I41" t="n">
-        <v>1.989389930489284</v>
+        <v>1.968503966571837</v>
       </c>
       <c r="J41" t="n">
         <v>55</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>30</v>
+        <v>29.52000045776367</v>
       </c>
       <c r="I43" t="n">
-        <v>2.833333333333333</v>
+        <v>2.879403749387316</v>
       </c>
       <c r="J43" t="n">
         <v>55</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>55.61999893188477</v>
+        <v>58.29999923706055</v>
       </c>
       <c r="I44" t="n">
-        <v>2.337288789940557</v>
+        <v>2.229845655252783</v>
       </c>
       <c r="J44" t="n">
         <v>55</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5.449999809265137</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I45" t="n">
-        <v>3.669724899072381</v>
+        <v>3.703703638293944</v>
       </c>
       <c r="J45" t="n">
         <v>55</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>20.63999938964844</v>
+        <v>20.6200008392334</v>
       </c>
       <c r="I46" t="n">
-        <v>4.844961383581868</v>
+        <v>4.849660326382303</v>
       </c>
       <c r="J46" t="n">
         <v>55</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8.5</v>
+        <v>8.939999580383301</v>
       </c>
       <c r="I48" t="n">
-        <v>2.823529411764706</v>
+        <v>2.684563884394612</v>
       </c>
       <c r="J48" t="n">
         <v>55</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>18.52000045776367</v>
+        <v>18.79500007629395</v>
       </c>
       <c r="I49" t="n">
-        <v>4.265658641864819</v>
+        <v>4.203245526965566</v>
       </c>
       <c r="J49" t="n">
         <v>55</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>4.550000190734863</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="I50" t="n">
-        <v>2.043955958273921</v>
+        <v>2.017353520749294</v>
       </c>
       <c r="J50" t="n">
         <v>55</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>32.02000045776367</v>
+        <v>32</v>
       </c>
       <c r="I51" t="n">
-        <v>1.093066817602552</v>
+        <v>1.09375</v>
       </c>
       <c r="J51" t="n">
         <v>55</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.919999957084656</v>
+        <v>1.945000052452087</v>
       </c>
       <c r="I52" t="n">
-        <v>3.125000069849194</v>
+        <v>3.084832821693614</v>
       </c>
       <c r="J52" t="n">
         <v>55</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>11.35000038146973</v>
+        <v>11.30000019073486</v>
       </c>
       <c r="I53" t="n">
-        <v>1.762114478220852</v>
+        <v>1.769911474550104</v>
       </c>
       <c r="J53" t="n">
         <v>55</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>5.599999904632568</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="I54" t="n">
-        <v>1.839285745608564</v>
+        <v>1.823008818786607</v>
       </c>
       <c r="J54" t="n">
         <v>55</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5.123000144958496</v>
+        <v>5.085000038146973</v>
       </c>
       <c r="I55" t="n">
-        <v>3.708764290919989</v>
+        <v>3.736479814643974</v>
       </c>
       <c r="J55" t="n">
         <v>55</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>9.694999694824219</v>
+        <v>9.824999809265137</v>
       </c>
       <c r="I56" t="n">
-        <v>4.45590524598601</v>
+        <v>4.396946650244379</v>
       </c>
       <c r="J56" t="n">
         <v>55</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>24.6200008392334</v>
+        <v>25.1200008392334</v>
       </c>
       <c r="I57" t="n">
-        <v>1.787164845660096</v>
+        <v>1.751592298168999</v>
       </c>
       <c r="J57" t="n">
         <v>55</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>6.78000020980835</v>
+        <v>6.920000076293945</v>
       </c>
       <c r="I58" t="n">
-        <v>6.932153177813626</v>
+        <v>6.791907439569159</v>
       </c>
       <c r="J58" t="n">
         <v>55</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>52.09999847412109</v>
+        <v>52.29999923706055</v>
       </c>
       <c r="I59" t="n">
-        <v>2.687140193862774</v>
+        <v>2.676864283791307</v>
       </c>
       <c r="J59" t="n">
         <v>55</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2.900000095367432</v>
+        <v>2.967999935150146</v>
       </c>
       <c r="I60" t="n">
-        <v>10.34482724601393</v>
+        <v>10.10781693244287</v>
       </c>
       <c r="J60" t="n">
         <v>55</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.230000019073486</v>
+        <v>3.109999895095825</v>
       </c>
       <c r="I61" t="n">
-        <v>1.08359132487063</v>
+        <v>1.125401967221661</v>
       </c>
       <c r="J61" t="n">
         <v>55</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>5.579999923706055</v>
+        <v>5.869999885559082</v>
       </c>
       <c r="I62" t="n">
-        <v>5.913978575484007</v>
+        <v>5.621805901765695</v>
       </c>
       <c r="J62" t="n">
         <v>55</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>45.22000122070312</v>
+        <v>45.54000091552734</v>
       </c>
       <c r="I63" t="n">
-        <v>1.570101682515966</v>
+        <v>1.559068919030078</v>
       </c>
       <c r="J63" t="n">
         <v>55</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>78.34999847412109</v>
+        <v>77.15000152587891</v>
       </c>
       <c r="I64" t="n">
-        <v>1.723037685119934</v>
+        <v>1.749837943356568</v>
       </c>
       <c r="J64" t="n">
         <v>55</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>3.480000019073486</v>
+        <v>3.586999893188477</v>
       </c>
       <c r="I65" t="n">
-        <v>4.885057444489921</v>
+        <v>4.739336634016104</v>
       </c>
       <c r="J65" t="n">
         <v>55</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>4.650000095367432</v>
+        <v>4.920000076293945</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8602150361211831</v>
+        <v>0.8130081174740657</v>
       </c>
       <c r="J66" t="n">
         <v>55</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>29.89999961853027</v>
+        <v>30.14999961853027</v>
       </c>
       <c r="I67" t="n">
-        <v>3.51170573042172</v>
+        <v>3.482587108739687</v>
       </c>
       <c r="J67" t="n">
         <v>55</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>17.44000053405762</v>
+        <v>17.29999923706055</v>
       </c>
       <c r="I68" t="n">
-        <v>2.17889901584532</v>
+        <v>2.196531888775771</v>
       </c>
       <c r="J68" t="n">
         <v>55</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>24.32999992370605</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="I69" t="n">
-        <v>2.466091253109241</v>
+        <v>2.409638591132698</v>
       </c>
       <c r="J69" t="n">
         <v>55</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>30</v>
+        <v>29.25</v>
       </c>
       <c r="I70" t="n">
-        <v>1.166666666666667</v>
+        <v>1.196581196581197</v>
       </c>
       <c r="J70" t="n">
         <v>55</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>2.308000087738037</v>
+        <v>2.302000045776367</v>
       </c>
       <c r="I71" t="n">
-        <v>11.26516421647167</v>
+        <v>11.29452627409975</v>
       </c>
       <c r="J71" t="n">
         <v>55</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>9.560000419616699</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I72" t="n">
-        <v>3.66108770541281</v>
+        <v>3.804347904958889</v>
       </c>
       <c r="J72" t="n">
         <v>48</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>4.760000228881836</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="I73" t="n">
-        <v>2.0168066257121</v>
+        <v>2.0600859043657</v>
       </c>
       <c r="J73" t="n">
         <v>48</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>14.18000030517578</v>
+        <v>14.23999977111816</v>
       </c>
       <c r="I74" t="n">
-        <v>3.526093012970508</v>
+        <v>3.511236011492847</v>
       </c>
       <c r="J74" t="n">
         <v>48</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>6.650000095367432</v>
+        <v>6.679999828338623</v>
       </c>
       <c r="I75" t="n">
-        <v>3.308270629247929</v>
+        <v>3.293413258286205</v>
       </c>
       <c r="J75" t="n">
         <v>48</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>3.349999904632568</v>
+        <v>3.375</v>
       </c>
       <c r="I76" t="n">
-        <v>4.776119538951121</v>
+        <v>4.74074074074074</v>
       </c>
       <c r="J76" t="n">
         <v>41</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>18.52000045776367</v>
+        <v>18.6200008392334</v>
       </c>
       <c r="I77" t="n">
-        <v>3.293736419667771</v>
+        <v>3.276047113352946</v>
       </c>
       <c r="J77" t="n">
         <v>41</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>11.94999980926514</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="I78" t="n">
-        <v>5.857740679269905</v>
+        <v>5.737705007736096</v>
       </c>
       <c r="J78" t="n">
         <v>41</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>8.670000076293945</v>
+        <v>8.630000114440918</v>
       </c>
       <c r="I79" t="n">
-        <v>5.888119902049838</v>
+        <v>5.915411277292573</v>
       </c>
       <c r="J79" t="n">
         <v>41</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>7.5</v>
+        <v>7.71999979019165</v>
       </c>
       <c r="I80" t="n">
-        <v>3.600000000000001</v>
+        <v>3.497409421474831</v>
       </c>
       <c r="J80" t="n">
         <v>41</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>4.730000019073486</v>
+        <v>4.800000190734863</v>
       </c>
       <c r="I81" t="n">
-        <v>7.399577137180606</v>
+        <v>7.291666376921876</v>
       </c>
       <c r="J81" t="n">
         <v>41</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>18.60000038146973</v>
+        <v>18.5</v>
       </c>
       <c r="I82" t="n">
-        <v>4.032257981818046</v>
+        <v>4.054054054054054</v>
       </c>
       <c r="J82" t="n">
         <v>41</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>10.19999980926514</v>
+        <v>9.880000114440918</v>
       </c>
       <c r="I83" t="n">
-        <v>4.215686353341016</v>
+        <v>4.352226670235545</v>
       </c>
       <c r="J83" t="n">
         <v>41</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>3.924999952316284</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="I84" t="n">
-        <v>3.821656097383634</v>
+        <v>3.76884420304397</v>
       </c>
       <c r="J84" t="n">
         <v>41</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>11.73999977111816</v>
+        <v>11.84000015258789</v>
       </c>
       <c r="I85" t="n">
-        <v>1.679463405826122</v>
+        <v>1.665278694754952</v>
       </c>
       <c r="J85" t="n">
         <v>41</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>25.60000038146973</v>
+        <v>25.64999961853027</v>
       </c>
       <c r="I86" t="n">
-        <v>4.296874935971575</v>
+        <v>4.288499089120179</v>
       </c>
       <c r="J86" t="n">
         <v>41</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>36.65000152587891</v>
+        <v>37.25</v>
       </c>
       <c r="I87" t="n">
-        <v>1.282401038013951</v>
+        <v>1.261744966442953</v>
       </c>
       <c r="J87" t="n">
         <v>41</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>22.89999961853027</v>
+        <v>22.85000038146973</v>
       </c>
       <c r="I89" t="n">
-        <v>1.179039320950559</v>
+        <v>1.181619236290942</v>
       </c>
       <c r="J89" t="n">
         <v>41</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>10.10000038146973</v>
+        <v>10.25</v>
       </c>
       <c r="I90" t="n">
-        <v>3.762376095521527</v>
+        <v>3.707317073170731</v>
       </c>
       <c r="J90" t="n">
         <v>41</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>27.85000038146973</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="I91" t="n">
-        <v>1.077199267112427</v>
+        <v>1.102941145533922</v>
       </c>
       <c r="J91" t="n">
         <v>41</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>6.190000057220459</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I92" t="n">
-        <v>2.584814192584127</v>
+        <v>2.640264051332858</v>
       </c>
       <c r="J92" t="n">
         <v>34</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1.320000052452087</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I95" t="n">
-        <v>5.30303009230682</v>
+        <v>5.263157724909606</v>
       </c>
       <c r="J95" t="n">
         <v>34</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>6.574999809265137</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="I96" t="n">
-        <v>7.604562958244149</v>
+        <v>7.633587563970797</v>
       </c>
       <c r="J96" t="n">
         <v>27</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>16.75</v>
+        <v>16.67000007629395</v>
       </c>
       <c r="I97" t="n">
-        <v>3.880597014925373</v>
+        <v>3.899220138123162</v>
       </c>
       <c r="J97" t="n">
         <v>27</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>11.65999984741211</v>
+        <v>11.65499973297119</v>
       </c>
       <c r="I98" t="n">
-        <v>4.631217899371165</v>
+        <v>4.633204739356426</v>
       </c>
       <c r="J98" t="n">
         <v>27</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>5.912000179290771</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="I99" t="n">
-        <v>1.691474914873843</v>
+        <v>1.663893447448422</v>
       </c>
       <c r="J99" t="n">
         <v>27</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>8.199999809265137</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>1.95121955758117</v>
+        <v>1.96078435039117</v>
       </c>
       <c r="J100" t="n">
         <v>27</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>283.1000061035156</v>
+        <v>279.2999877929688</v>
       </c>
       <c r="I101" t="n">
-        <v>1.276933918072108</v>
+        <v>1.294307253131576</v>
       </c>
       <c r="J101" t="n">
         <v>27</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>26.20000076293945</v>
+        <v>25.5</v>
       </c>
       <c r="I102" t="n">
-        <v>5.190839543500142</v>
+        <v>5.333333333333334</v>
       </c>
       <c r="J102" t="n">
         <v>27</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>12.84000015258789</v>
+        <v>12.64999961853027</v>
       </c>
       <c r="I103" t="n">
-        <v>4.556074712211696</v>
+        <v>4.624506068309016</v>
       </c>
       <c r="J103" t="n">
         <v>27</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>16.04999923706055</v>
+        <v>16.34499931335449</v>
       </c>
       <c r="I104" t="n">
-        <v>3.925233831446465</v>
+        <v>3.854389883548455</v>
       </c>
       <c r="J104" t="n">
         <v>27</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>94.90000152587891</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="I105" t="n">
-        <v>0.9483666865427531</v>
+        <v>0.9491668454931738</v>
       </c>
       <c r="J105" t="n">
         <v>27</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>61.61999893188477</v>
+        <v>61.52999877929688</v>
       </c>
       <c r="I106" t="n">
-        <v>2.792599853664694</v>
+        <v>2.796684599608673</v>
       </c>
       <c r="J106" t="n">
         <v>27</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>22.39999961853027</v>
+        <v>23.39999961853027</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6250000106436868</v>
+        <v>0.5982906080440067</v>
       </c>
       <c r="J107" t="n">
         <v>20</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1.894999980926514</v>
+        <v>1.929999947547913</v>
       </c>
       <c r="I109" t="n">
-        <v>1.794195268718501</v>
+        <v>1.7616580789651</v>
       </c>
       <c r="J109" t="n">
         <v>6</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>22.52000045776367</v>
+        <v>22.96999931335449</v>
       </c>
       <c r="I110" t="n">
-        <v>1.154529283814318</v>
+        <v>1.131911222343133</v>
       </c>
       <c r="J110" t="n">
         <v>-1</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>27</v>
+        <v>27.51000022888184</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.327153759546363</v>
       </c>
       <c r="J111" t="n">
         <v>-1</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>50.54999923706055</v>
+        <v>49.97999954223633</v>
       </c>
       <c r="I112" t="n">
-        <v>1.285855607933333</v>
+        <v>1.300520219994616</v>
       </c>
       <c r="J112" t="n">
         <v>-29</v>
@@ -5716,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C326"/>
+  <dimension ref="A1:C316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6453,7 +6453,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6470,7 +6470,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6487,7 +6487,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6504,7 +6504,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6521,7 +6521,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6538,7 +6538,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6548,14 +6548,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6565,14 +6565,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6633,14 +6633,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6650,14 +6650,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6667,14 +6667,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6691,7 +6691,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6708,7 +6708,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6742,7 +6742,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6793,7 +6793,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6888,14 +6888,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6946,7 +6946,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6963,7 +6963,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6980,7 +6980,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6990,14 +6990,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7007,14 +7007,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7116,7 +7116,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7133,7 +7133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7184,7 +7184,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7201,7 +7201,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7218,7 +7218,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7235,7 +7235,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7303,7 +7303,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7320,7 +7320,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7337,7 +7337,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7354,7 +7354,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7371,7 +7371,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7388,7 +7388,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7405,7 +7405,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7422,7 +7422,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7439,7 +7439,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7456,7 +7456,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7490,7 +7490,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7507,7 +7507,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7524,7 +7524,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7534,14 +7534,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7575,7 +7575,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7609,7 +7609,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7626,7 +7626,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7643,7 +7643,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7660,7 +7660,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7677,7 +7677,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7694,7 +7694,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7711,7 +7711,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7745,7 +7745,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7755,14 +7755,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7779,7 +7779,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7796,7 +7796,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7806,14 +7806,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7830,7 +7830,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7847,7 +7847,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7864,7 +7864,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7881,7 +7881,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7898,7 +7898,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7915,7 +7915,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7932,7 +7932,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7949,7 +7949,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7966,7 +7966,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7983,7 +7983,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8000,7 +8000,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8010,14 +8010,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8034,7 +8034,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8051,7 +8051,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8085,7 +8085,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8095,14 +8095,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8119,7 +8119,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8136,7 +8136,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8153,7 +8153,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8170,7 +8170,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8187,29 +8187,29 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8221,29 +8221,29 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8255,12 +8255,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8272,29 +8272,29 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8306,12 +8306,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8323,12 +8323,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8340,12 +8340,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8367,14 +8367,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8391,7 +8391,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8401,14 +8401,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8425,7 +8425,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8442,7 +8442,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -8452,14 +8452,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8476,7 +8476,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8486,14 +8486,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8510,7 +8510,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8527,7 +8527,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8544,7 +8544,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8561,7 +8561,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8578,7 +8578,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8595,7 +8595,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8612,7 +8612,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8629,7 +8629,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8656,14 +8656,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8680,7 +8680,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8697,7 +8697,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8714,7 +8714,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8731,7 +8731,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8741,14 +8741,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8758,36 +8758,36 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8799,46 +8799,46 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8850,63 +8850,63 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8918,29 +8918,29 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8952,12 +8952,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8969,46 +8969,46 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9020,80 +9020,80 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -9105,114 +9105,114 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9224,46 +9224,46 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9275,29 +9275,29 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9309,12 +9309,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9326,58 +9326,58 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -9387,14 +9387,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -9411,7 +9411,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -9428,7 +9428,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9455,14 +9455,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -9472,14 +9472,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -9506,14 +9506,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -9530,12 +9530,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -9547,80 +9547,80 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -9632,29 +9632,29 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -9666,41 +9666,41 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -9710,14 +9710,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -9727,14 +9727,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -9751,7 +9751,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -9761,14 +9761,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -9778,14 +9778,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -9795,14 +9795,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -9819,7 +9819,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -9836,7 +9836,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -9853,7 +9853,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -9863,36 +9863,36 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9904,12 +9904,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9921,29 +9921,29 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9955,12 +9955,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9972,46 +9972,46 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -10023,12 +10023,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -10040,97 +10040,97 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10142,12 +10142,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -10159,29 +10159,29 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -10193,29 +10193,29 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10227,24 +10227,24 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -10254,19 +10254,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10278,12 +10278,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10295,12 +10295,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10312,80 +10312,80 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10397,12 +10397,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10414,12 +10414,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10431,7 +10431,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -10441,14 +10441,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -10458,14 +10458,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -10475,14 +10475,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -10492,14 +10492,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -10516,7 +10516,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -10526,14 +10526,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -10550,7 +10550,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10567,7 +10567,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10584,7 +10584,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -10594,14 +10594,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -10611,19 +10611,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10635,12 +10635,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10652,12 +10652,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10669,12 +10669,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10686,12 +10686,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10703,12 +10703,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10720,63 +10720,63 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10788,7 +10788,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -10805,7 +10805,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -10822,7 +10822,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -10832,14 +10832,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -10856,7 +10856,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10873,7 +10873,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -10883,14 +10883,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -10907,7 +10907,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -10924,7 +10924,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -10941,7 +10941,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -10958,7 +10958,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10975,7 +10975,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -10992,7 +10992,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -11009,7 +11009,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -11026,7 +11026,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -11043,7 +11043,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -11060,7 +11060,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -11077,7 +11077,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -11086,176 +11086,6 @@
         </is>
       </c>
       <c r="C316" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>REPLY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Technoprobe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>gAIn360 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Egomnia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>Directa SIM S.P.A.</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -11272,314 +11102,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DiaSorin S.p.A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0003492391</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>55.61999893188477</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2.337288789940557</v>
-      </c>
-      <c r="I2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>F.I.L.A. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0004967292</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2.823529411764706</v>
-      </c>
-      <c r="I3" t="n">
-        <v>55</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IREN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0003027817</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2.447999954223633</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1386</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>5.661764811754503</v>
-      </c>
-      <c r="I4" t="n">
-        <v>90</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>POWERSOFT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0005353815</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>15.64999961853027</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>4.984025680591368</v>
-      </c>
-      <c r="I5" t="n">
-        <v>90</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pattern S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0005378143</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>3.230000019073486</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1.08359132487063</v>
-      </c>
-      <c r="I6" t="n">
-        <v>55</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RAI WAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT0005054967</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5.579999923706055</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>5.913978575484007</v>
-      </c>
-      <c r="I7" t="n">
-        <v>55</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11590,571 +11115,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AMPLIFON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Alerion Clean Power S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Bper Banca S.P.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DE' LONGHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Directa SIM S.P.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Egomnia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Esprinet S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GEFRAN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Impianti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>OPS Italia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>POWERSOFT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Predict S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REPLY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Technoprobe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>gAIn360 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>